--- a/nonprofit_employee_forms/008_donor_retention_resource_request_form--nonprofit_employee_forms.xlsx
+++ b/nonprofit_employee_forms/008_donor_retention_resource_request_form--nonprofit_employee_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -784,8 +784,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -813,12 +813,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'financial_support',_'label':_'financial_support'}</t>
+          <t>financial_support</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Financial Support', 'label': 'Financial Support'}</t>
+          <t>Financial Support</t>
         </is>
       </c>
     </row>
@@ -830,12 +830,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'volunteer_support',_'label':_'volunteer_support'}</t>
+          <t>volunteer_support</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Volunteer Support', 'label': 'Volunteer Support'}</t>
+          <t>Volunteer Support</t>
         </is>
       </c>
     </row>
@@ -847,12 +847,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'expert_advice',_'label':_'expert_advice'}</t>
+          <t>expert_advice</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Expert Advice', 'label': 'Expert Advice'}</t>
+          <t>Expert Advice</t>
         </is>
       </c>
     </row>
@@ -864,12 +864,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'phone',_'label':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Phone', 'label': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -881,12 +881,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'email',_'label':_'email',_'hint':_'we_will_use_this_for_all_future_communication.'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Email', 'label': 'Email', 'hint': 'We will use this for all future communication.'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -898,12 +898,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'mail',_'label':_'mail',_'hint':_'we_will_not_use_this_for_future_communication.'}</t>
+          <t>mail</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Mail', 'label': 'Mail', 'hint': 'We will not use this for future communication.'}</t>
+          <t>Mail</t>
         </is>
       </c>
     </row>
@@ -915,12 +915,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'submit_request',_'label':_'submit_request'}</t>
+          <t>submit_request</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Submit Request', 'label': 'Submit Request'}</t>
+          <t>Submit Request</t>
         </is>
       </c>
     </row>
@@ -932,12 +932,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'cancel_request',_'label':_'cancel_request'}</t>
+          <t>cancel_request</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Cancel Request', 'label': 'Cancel Request'}</t>
+          <t>Cancel Request</t>
         </is>
       </c>
     </row>
